--- a/src/attributions/attributions_saliency_traj_302.xlsx
+++ b/src/attributions/attributions_saliency_traj_302.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1275099962949753</v>
+        <v>0.005122112110257149</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2907246053218842</v>
+        <v>0.0009265051339752972</v>
       </c>
       <c r="C3" t="n">
-        <v>1.120352506637573</v>
+        <v>0.002264084992930293</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02225790917873383</v>
+        <v>0.001557793002575636</v>
       </c>
       <c r="E3" t="n">
-        <v>0.411358654499054</v>
+        <v>0.001651780912652612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2138659209012985</v>
+        <v>0.001598254195414484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4823006987571716</v>
+        <v>0.001416758866980672</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06739357113838196</v>
+        <v>0.00301643880084157</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1376900672912598</v>
+        <v>0.0006485008634626865</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2021587491035461</v>
+        <v>0.005468461196869612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3801884949207306</v>
+        <v>0.002036726800724864</v>
       </c>
       <c r="L3" t="n">
-        <v>1.096622586250305</v>
+        <v>0.002095094881951809</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2813665568828583</v>
+        <v>0.005421695299446583</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2669095098972321</v>
+        <v>0.005918240174651146</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02522666752338409</v>
+        <v>0.001261104247532785</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5913079977035522</v>
+        <v>0.001168786664493382</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08642929047346115</v>
+        <v>0.003255791962146759</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3025875687599182</v>
+        <v>5.015433998778462e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03176233917474747</v>
+        <v>0.0006133677088655531</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2261158227920532</v>
+        <v>0.001438235398381948</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3121541738510132</v>
+        <v>0.0007619454408995807</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1771288216114044</v>
+        <v>3.171747084707022e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1252261847257614</v>
+        <v>0.0002222149632871151</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2899809181690216</v>
+        <v>0.0004636872909031808</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08097237348556519</v>
+        <v>8.036397775867954e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01932928897440434</v>
+        <v>0.0003782807034440339</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1792004406452179</v>
+        <v>0.0003258153155911714</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.123588889837265</v>
+        <v>0.00186211068648845</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03718731552362442</v>
+        <v>1.492232604505261e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1589305996894836</v>
+        <v>0.0004499622154980898</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09841562807559967</v>
+        <v>0.001564617035910487</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2229645550251007</v>
+        <v>0.0007774960831739008</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.01729998178780079</v>
+        <v>0.001593552296981215</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.1567918956279755</v>
+        <v>0.0006240527145564556</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1511141657829285</v>
+        <v>0.0005197552964091301</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1863121688365936</v>
+        <v>0.0004877124156337231</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0688093900680542</v>
+        <v>0.0004627820453606546</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.214530885219574</v>
+        <v>0.001524860737845302</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1406868994235992</v>
+        <v>0.0009989498648792505</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.03808311372995377</v>
+        <v>0.0004139896191190928</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.3108270466327667</v>
+        <v>0.000663089333102107</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1126691699028015</v>
+        <v>1.064679236151278e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.2210482060909271</v>
+        <v>3.491950337775052e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.08875632286071777</v>
+        <v>0.0001784871565178037</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.05440183728933334</v>
+        <v>0.0004425263905432075</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1228953674435616</v>
+        <v>0.002581648528575897</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.118701696395874</v>
+        <v>0.001621512928977609</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3328729867935181</v>
+        <v>0.001115640858188272</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.04838508367538452</v>
+        <v>0.001691294251941144</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.167746290564537</v>
+        <v>0.003127977484837174</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.07486063987016678</v>
+        <v>0.0008479287498630583</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.4695133566856384</v>
+        <v>0.0003508258669171482</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1270675510168076</v>
+        <v>0.0008505274308845401</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.3186812698841095</v>
+        <v>0.0003985212533734739</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.02667922154068947</v>
+        <v>0.0004220943083055317</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.5500052571296692</v>
+        <v>0.0005317303584888577</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.4954731166362762</v>
+        <v>0.001044877455569804</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2748160362243652</v>
+        <v>0.0002000137756112963</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.04686304926872253</v>
+        <v>0.002185220830142498</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.3818437159061432</v>
+        <v>0.001305141369812191</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.07580415904521942</v>
+        <v>0.0002261495828861371</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.2279016077518463</v>
+        <v>0.0005515313823707402</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.4411207735538483</v>
+        <v>0.0008307643001899123</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1482608318328857</v>
+        <v>0.001809019013307989</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.3366959095001221</v>
+        <v>0.0007794981356710196</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.2237430661916733</v>
+        <v>0.001135267782956362</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.2256623059511185</v>
+        <v>0.001313929446041584</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0273804534226656</v>
+        <v>0.0005272096022963524</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1851815432310104</v>
+        <v>8.176738629117608e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.2350282818078995</v>
+        <v>0.0002554243837948889</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.05110578984022141</v>
+        <v>0.001071202219463885</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1348258852958679</v>
+        <v>5.933910142630339e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.03173194825649261</v>
+        <v>0.002067839493975043</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1665272414684296</v>
+        <v>0.00107739819213748</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.09498650580644608</v>
+        <v>0.00189410662278533</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.2414930909872055</v>
+        <v>0.0002016104117501527</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.07159003615379333</v>
+        <v>0.001921082730405033</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2913358211517334</v>
+        <v>0.0003349341568537056</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1861197054386139</v>
+        <v>0.0003774544165935367</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1036711931228638</v>
+        <v>0.0005525118904188275</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.3120754957199097</v>
+        <v>0.00129448773805052</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.03618726134300232</v>
+        <v>0.00111930281855166</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.06188903003931046</v>
+        <v>0.0004120582307223231</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1780202090740204</v>
+        <v>0.0002855751081369817</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.08966707438230515</v>
+        <v>0.0005101143615320325</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01792521961033344</v>
+        <v>0.0011294677387923</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.04539171233773232</v>
+        <v>7.910098065622151e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.02015399932861328</v>
+        <v>0.000247075833613053</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.03572390973567963</v>
+        <v>0.000383297010557726</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.009072897024452686</v>
+        <v>5.672074621543288e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0911189392209053</v>
+        <v>0.0007555895135737956</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.09240122139453888</v>
+        <v>0.001027235412038863</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1293380260467529</v>
+        <v>0.001613554661162198</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1386013925075531</v>
+        <v>0.001709126168861985</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.4996147751808167</v>
+        <v>0.0003165971720591187</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.09808344393968582</v>
+        <v>0.0008091425988823175</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.06920135021209717</v>
+        <v>0.001556710689328611</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1730359941720963</v>
+        <v>0.00212970795109868</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.05454296246170998</v>
+        <v>0.0003846063045784831</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.02162038721144199</v>
+        <v>0.001117941690608859</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.08640578389167786</v>
+        <v>0.0008183922618627548</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.2058627009391785</v>
+        <v>0.0005929894978180528</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0671471506357193</v>
+        <v>0.0003311273467261344</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.04155141487717628</v>
+        <v>0.0007587932632304728</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.04660400375723839</v>
+        <v>4.101687227375805e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.05890688300132751</v>
+        <v>0.0001216824457515031</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.04206645488739014</v>
+        <v>0.000389498716685921</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.04037249833345413</v>
+        <v>8.519894618075341e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2863432466983795</v>
+        <v>0.001027224934659898</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2010102272033691</v>
+        <v>0.004823186434805393</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.7464808225631714</v>
+        <v>0.0005706304800696671</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.4448232054710388</v>
+        <v>0.00104145216755569</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.004152677953243256</v>
+        <v>0.00137159856967628</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2443468123674393</v>
+        <v>0.002759286900982261</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.06340733170509338</v>
+        <v>0.0004368260269984603</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07357786595821381</v>
+        <v>0.0001813857816159725</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2156695127487183</v>
+        <v>0.001881138305179775</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.04707138240337372</v>
+        <v>0.001168851740658283</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.1179615408182144</v>
+        <v>0.0008097753743641078</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.03943063318729401</v>
+        <v>0.001143132336437702</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.01695594191551208</v>
+        <v>0.0005647863727062941</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2648507356643677</v>
+        <v>0.001460643252357841</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.02506295591592789</v>
+        <v>0.0002107172040268779</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.224205955862999</v>
+        <v>0.0004788704391103238</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.2154391407966614</v>
+        <v>0.0001655613450566307</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.1660135984420776</v>
+        <v>0.0002172025706386194</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09513924270868301</v>
+        <v>0.0003482243046164513</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.09387359023094177</v>
+        <v>0.0006603485089726746</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.2048076540231705</v>
+        <v>0.001542942714877427</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.03593111038208008</v>
+        <v>0.000582724460400641</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1190040558576584</v>
+        <v>0.0005636385758407414</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.06689904630184174</v>
+        <v>0.0005570465000346303</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.02728764712810516</v>
+        <v>5.436549690784886e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.2322729676961899</v>
+        <v>0.0005991603247821331</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.05626519396901131</v>
+        <v>0.0003537932061590254</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.03879791498184204</v>
+        <v>0.001055848901160061</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.04712831228971481</v>
+        <v>0.0009505134075880051</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2966936826705933</v>
+        <v>5.35649960511364e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2108888924121857</v>
+        <v>3.978100721724331e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.1092288717627525</v>
+        <v>0.0009146996890194714</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.2781693637371063</v>
+        <v>0.0003033257089555264</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.08425827324390411</v>
+        <v>0.0006970832473598421</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0330217182636261</v>
+        <v>0.0006473266985267401</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.06988005340099335</v>
+        <v>0.0003899946459569037</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.02085930481553078</v>
+        <v>0.0001846866507548839</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1105480492115021</v>
+        <v>0.0009093229309655726</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.1313370615243912</v>
+        <v>0.0003354361688252538</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.03989578038454056</v>
+        <v>0.001047455938532948</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01007547322660685</v>
+        <v>0.00147137395106256</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.004111802205443382</v>
+        <v>0.0008347613620571792</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.2590011358261108</v>
+        <v>1.304913894273341e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.111118383705616</v>
+        <v>0.0006524703348986804</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.2113082259893417</v>
+        <v>0.0007995289633981884</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.05296022072434425</v>
+        <v>0.0009293345501646399</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.003745406866073608</v>
+        <v>0.0009354365174658597</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.2366422116756439</v>
+        <v>0.0007327423663809896</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.09018193185329437</v>
+        <v>0.0002155987604055554</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0337238572537899</v>
+        <v>0.001038480899296701</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.08932929486036301</v>
+        <v>0.0002325755631318316</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.08399002254009247</v>
+        <v>0.0002276873565278947</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.02607549540698528</v>
+        <v>0.000629821268375963</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.0652485266327858</v>
+        <v>0.0002251960540888831</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.2415493875741959</v>
+        <v>0.003502997569739819</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.03769684210419655</v>
+        <v>0.0003335622604936361</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.07757911086082458</v>
+        <v>6.685026164632291e-05</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.03723198547959328</v>
+        <v>0.00194806233048439</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.07181370258331299</v>
+        <v>0.001034890534356236</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.06981407850980759</v>
+        <v>0.0003843166923616081</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.03530574962496758</v>
+        <v>0.0004536898341029882</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.06214076653122902</v>
+        <v>0.0002019114035647362</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.02189107425510883</v>
+        <v>0.000138340430567041</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1742090582847595</v>
+        <v>0.001469137030653656</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.02226416021585464</v>
+        <v>0.00314912898465991</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.08664111793041229</v>
+        <v>0.002448954386636615</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.0006770268082618713</v>
+        <v>0.004891029093414545</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01899793930351734</v>
+        <v>0.0001507035631220788</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.3484292328357697</v>
+        <v>0.0009649396524764597</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.2889387607574463</v>
+        <v>0.001741827931255102</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.3074528276920319</v>
+        <v>0.0006025314214639366</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.07208671420812607</v>
+        <v>0.0002802564995363355</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.1640705317258835</v>
+        <v>0.002000597305595875</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.1723926812410355</v>
+        <v>0.001842935336753726</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.2798144817352295</v>
+        <v>0.00010382058826508</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.2856511175632477</v>
+        <v>2.022508124355227e-05</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.1393889933824539</v>
+        <v>0.0007431391859427094</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.131408616900444</v>
+        <v>0.0003340230614412576</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.1338288933038712</v>
+        <v>0.0005523021100088954</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.05502945184707642</v>
+        <v>0.0004408314998727292</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.08116364479064941</v>
+        <v>0.0003033661341760308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.000734275090508163</v>
+        <v>0.0004777840222232044</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0060981260612607</v>
+        <v>0.002050134353339672</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003294008783996105</v>
+        <v>6.739867967553437e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003615273861214519</v>
+        <v>0.002036732854321599</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001809737179428339</v>
+        <v>0.0006150614353828132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001598241971805692</v>
+        <v>0.0006250208825804293</v>
       </c>
       <c r="G4" t="n">
-        <v>1.739902654662728e-05</v>
+        <v>0.001021463889628649</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0002608297509141266</v>
+        <v>0.0006169232074171305</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005637097638100386</v>
+        <v>8.212691318476573e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009465407929383218</v>
+        <v>0.0004017356841359288</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004009354393929243</v>
+        <v>0.002105903346091509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005067890742793679</v>
+        <v>0.0002288235700689256</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002971237059682608</v>
+        <v>0.002798136323690414</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002803556621074677</v>
+        <v>0.0008566195610910654</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002163685625419021</v>
+        <v>0.0003236321499571204</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000536006991751492</v>
+        <v>0.001245006918907166</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008780098287388682</v>
+        <v>0.0001611486804904416</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0004193378263153136</v>
+        <v>3.044084951397963e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001207015884574503</v>
+        <v>0.0002340931096114218</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009157985914498568</v>
+        <v>6.707851571263745e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001732223900035024</v>
+        <v>3.726243448909372e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007235519005917013</v>
+        <v>5.603714816970751e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>8.31842771731317e-05</v>
+        <v>0.0001557670329930261</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0007687276229262352</v>
+        <v>0.0004575071798171848</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0009807548485696316</v>
+        <v>0.0001393310230923817</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0001941186055773869</v>
+        <v>0.0003875847614835948</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0003349266189616174</v>
+        <v>0.0003832676156889647</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003846553445328027</v>
+        <v>0.0003128866374026984</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0007297912379726768</v>
+        <v>0.0001108411815948784</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.356792826205492e-06</v>
+        <v>0.0002108626795234159</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0001616525842109695</v>
+        <v>4.532001912593842e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0008440242381766438</v>
+        <v>0.0001982925896300003</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.16057344712317e-05</v>
+        <v>0.0003625820390880108</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.838497938588262e-05</v>
+        <v>6.452077650465071e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0001189328322652727</v>
+        <v>0.000154765453771688</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0003575562732294202</v>
+        <v>0.0001839837350416929</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0002509646292310208</v>
+        <v>0.0003675967454910278</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0006444248137995601</v>
+        <v>0.0005251048714853823</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.054114520433359e-05</v>
+        <v>0.000243316957494244</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0002746900136116892</v>
+        <v>0.0004235969390720129</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0003853206872008741</v>
+        <v>5.092403443995863e-05</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0008106486056931317</v>
+        <v>0.0003595153684727848</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0002139868156518787</v>
+        <v>0.0002913904318120331</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0001262456498807296</v>
+        <v>5.360989962355234e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0004099675861652941</v>
+        <v>6.36164186289534e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.00061027955962345</v>
+        <v>0.0001165185385616496</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.004390847869217396</v>
+        <v>0.001173947588540614</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.717754250625148e-05</v>
+        <v>0.0001279494608752429</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001301145413890481</v>
+        <v>0.001059935428202152</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004586798895616084</v>
+        <v>0.001445083878934383</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0001658593391766772</v>
+        <v>0.0002169876825064421</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0006165068480186164</v>
+        <v>9.432915248908103e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0004570697783492506</v>
+        <v>0.0001845066144596785</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0003572069981601089</v>
+        <v>0.000135218579089269</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004733743844553828</v>
+        <v>0.0003898729046341032</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0008347969851456583</v>
+        <v>0.0001267424231627956</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0006439274875447154</v>
+        <v>0.0001621755945961922</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0003247744753025472</v>
+        <v>0.0002622129686642438</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.002096656244248152</v>
+        <v>0.0006205723038874567</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001277129864320159</v>
+        <v>0.0003197394835297018</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.000564660644158721</v>
+        <v>0.0002402866666670889</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0005949686164967716</v>
+        <v>0.000541411223821342</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0001599416136741638</v>
+        <v>0.0004114449257031083</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0007642609416507185</v>
+        <v>2.845426934072748e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0007169045857153833</v>
+        <v>1.634154614293948e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0001342146715614945</v>
+        <v>1.002589579002233e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0005376500776037574</v>
+        <v>0.0004314276447985321</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0004413769056554884</v>
+        <v>0.0001564057602081448</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0003073950065299869</v>
+        <v>8.429104491369799e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>5.104788579046726e-05</v>
+        <v>2.032505835813936e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0001588537561474368</v>
+        <v>0.0002364627871429548</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0004033851728308946</v>
+        <v>4.781645839102566e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0004922267398796976</v>
+        <v>0.0001590696774655953</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002229236532002687</v>
+        <v>0.0006827310426160693</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001444993977202103</v>
+        <v>7.253845251398161e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0006451751687563956</v>
+        <v>0.001161751337349415</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0003927495563402772</v>
+        <v>0.0003934429259970784</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001274876412935555</v>
+        <v>0.0002686305670067668</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0001571081229485571</v>
+        <v>0.0002136607799911872</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0004048406262882054</v>
+        <v>0.0002129110071109608</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0004067812697030604</v>
+        <v>0.0002471346233505756</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0003974904248025268</v>
+        <v>7.286329491762444e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.000992695102468133</v>
+        <v>0.0005697064334526658</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0002646553621161729</v>
+        <v>1.327138306805864e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0003213834424968809</v>
+        <v>0.0007203662535175681</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0001058492052834481</v>
+        <v>0.0001216270320583135</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0004233317449688911</v>
+        <v>4.996824645786546e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0002169338258681819</v>
+        <v>9.264195978175849e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>7.666624151170254e-05</v>
+        <v>2.286249036842491e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0002613801043480635</v>
+        <v>7.519995415350422e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0004363793996162713</v>
+        <v>0.0002013483899645507</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.000193870990187861</v>
+        <v>0.0006071093957871199</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0004598875239025801</v>
+        <v>0.0004875795857515186</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.001036974717862904</v>
+        <v>0.0009244020329788327</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.000873336277436465</v>
+        <v>6.112491973908618e-06</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0006388828041963279</v>
+        <v>0.0001173585260403343</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0005110881756991148</v>
+        <v>0.0001343617477687076</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001443127170205116</v>
+        <v>0.0002481921401340514</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.664929732214659e-05</v>
+        <v>0.0003108988748863339</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003764014400076121</v>
+        <v>6.651095463894308e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0007874935399740934</v>
+        <v>0.0006036949343979359</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0002774221356958151</v>
+        <v>4.001378692919388e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0006760865217074752</v>
+        <v>0.0007723176386207342</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001237239048350602</v>
+        <v>0.0001940601214300841</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0005331301945261657</v>
+        <v>7.70407568779774e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0001602846896275878</v>
+        <v>0.000148512001032941</v>
       </c>
       <c r="DC4" t="n">
-        <v>6.792964995838702e-05</v>
+        <v>2.00547838176135e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.000170137092936784</v>
+        <v>0.0001093090249923989</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0002662473125383258</v>
+        <v>8.664532651891932e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001149205258116126</v>
+        <v>0.0005175725091248751</v>
       </c>
       <c r="DG4" t="n">
-        <v>4.572408579406328e-05</v>
+        <v>0.0002486197627149522</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.001302980934269726</v>
+        <v>0.0007414233405143023</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001222591381520033</v>
+        <v>0.0001140222520916723</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0003982242778874934</v>
+        <v>0.0006929194205440581</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0005008739535696805</v>
+        <v>0.0002065990265691653</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0009506340138614178</v>
+        <v>0.0008667641086503863</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0002604819310363382</v>
+        <v>0.000297104474157095</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0008785179816186428</v>
+        <v>0.0001336837303824723</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.000444976263679564</v>
+        <v>0.0003392099752090871</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0003004763275384903</v>
+        <v>1.547786814626306e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0002553146332502365</v>
+        <v>0.0002854485937859863</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.134214734425768e-05</v>
+        <v>7.459730841219425e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0006151185370981693</v>
+        <v>0.0002327789843548089</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0001306442718487233</v>
+        <v>0.0003490021335892379</v>
       </c>
       <c r="DU4" t="n">
-        <v>3.111733531113714e-05</v>
+        <v>0.0004128899890929461</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0003165396919939667</v>
+        <v>0.0008433493203483522</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0003741017717402428</v>
+        <v>9.60524776019156e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>8.043169509619474e-05</v>
+        <v>0.0001625411678105593</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0007980871014297009</v>
+        <v>1.043198790284805e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003971831465605646</v>
+        <v>0.0003771138726733625</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0006149110267870128</v>
+        <v>0.0001864446967374533</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0006319646490737796</v>
+        <v>0.0006408614572137594</v>
       </c>
       <c r="EC4" t="n">
-        <v>4.376210563350469e-05</v>
+        <v>1.333008913206868e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0002751495048869401</v>
+        <v>0.001184998196549714</v>
       </c>
       <c r="EE4" t="n">
-        <v>7.939474744489416e-05</v>
+        <v>0.0004779185983352363</v>
       </c>
       <c r="EF4" t="n">
-        <v>5.308965046424419e-05</v>
+        <v>0.0003249982837587595</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.000346713699400425</v>
+        <v>0.0004217074310872704</v>
       </c>
       <c r="EH4" t="n">
-        <v>4.437574534676969e-05</v>
+        <v>0.0002104055020026863</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.000252785044722259</v>
+        <v>0.0005401435773819685</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0003433784877415746</v>
+        <v>9.857579425442964e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0003741236578207463</v>
+        <v>9.618321200832725e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0003228120331186801</v>
+        <v>8.144948515109718e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0003249176079407334</v>
+        <v>1.934693318617065e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>6.661532097496092e-05</v>
+        <v>3.830967762041837e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0003608527476899326</v>
+        <v>0.0001700677239568904</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0007579320226795971</v>
+        <v>0.000614666030742228</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0001487106346758083</v>
+        <v>1.683760638115928e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0005194633267819881</v>
+        <v>0.0006373160285875201</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0004501616058405489</v>
+        <v>0.0002850576711352915</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001988430507481098</v>
+        <v>0.0003844048769678921</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0001432480639778078</v>
+        <v>0.0002549596247263253</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0001946559350471944</v>
+        <v>7.611335604451597e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>9.916462295223027e-05</v>
+        <v>0.0004540745285339653</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0002712067507673055</v>
+        <v>8.883674308890477e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0008338360348716378</v>
+        <v>0.0006529571255668998</v>
       </c>
       <c r="EZ4" t="n">
-        <v>4.873488433077e-05</v>
+        <v>6.095979188103229e-06</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0005086282035335898</v>
+        <v>0.0008221687749028206</v>
       </c>
       <c r="FB4" t="n">
-        <v>2.698729076655582e-05</v>
+        <v>0.0001483518717577681</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0005391970044001937</v>
+        <v>7.338241266552359e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0002427248255116865</v>
+        <v>0.0001655369997024536</v>
       </c>
       <c r="FE4" t="n">
-        <v>9.788115858100355e-05</v>
+        <v>0.0001198464742628857</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0002639734593685716</v>
+        <v>0.0001411023986293003</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0001936866901814938</v>
+        <v>0.000117149313155096</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0003356857341714203</v>
+        <v>0.0003889085492119193</v>
       </c>
       <c r="FI4" t="n">
-        <v>6.526662036776543e-05</v>
+        <v>0.0003388375916983932</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.000881187675986439</v>
+        <v>0.0003090712707489729</v>
       </c>
       <c r="FK4" t="n">
-        <v>7.547351560788229e-05</v>
+        <v>0.0001395437866449356</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0002337482874281704</v>
+        <v>0.0002428914449410513</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0002826774725690484</v>
+        <v>0.0003161419299431145</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0001512466988060623</v>
+        <v>0.0003199904458597302</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0006786618614569306</v>
+        <v>0.0004216510569676757</v>
       </c>
       <c r="FP4" t="n">
-        <v>8.155501564033329e-05</v>
+        <v>0.0003892210079357028</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0003084700147155672</v>
+        <v>0.0008379090577363968</v>
       </c>
       <c r="FR4" t="n">
-        <v>5.525507003767416e-05</v>
+        <v>9.824155131354928e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0009270606678910553</v>
+        <v>0.000826879870146513</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.001601481577381492</v>
+        <v>0.0001189754329971038</v>
       </c>
       <c r="FU4" t="n">
-        <v>4.50640800409019e-06</v>
+        <v>0.000463765871245414</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0002493669744580984</v>
+        <v>9.780729305930436e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0003380689886398613</v>
+        <v>0.0002822620735969394</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0003749665629584342</v>
+        <v>0.000512459606397897</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0005188843351788819</v>
+        <v>0.0004326281487010419</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0005121005815453827</v>
+        <v>0.0001851779816206545</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0001284245809074491</v>
+        <v>0.0001005467347567901</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0001870603009592742</v>
+        <v>0.0006159909535199404</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.000850675452966243</v>
+        <v>0.0009612818830646574</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0007417001179419458</v>
+        <v>0.0002277428866364062</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.001117191510275006</v>
+        <v>0.000457127986010164</v>
       </c>
       <c r="GF4" t="n">
-        <v>3.855382965411991e-05</v>
+        <v>0.0003787532914429903</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0002400521334493533</v>
+        <v>0.0001529749861219898</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0004430944682098925</v>
+        <v>0.01102812122553587</v>
       </c>
       <c r="B5" t="n">
-        <v>0.004046596586704254</v>
+        <v>0.0230415016412735</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000800918263848871</v>
+        <v>0.00184315862134099</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001823783153668046</v>
+        <v>0.002585934940725565</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005211768671870232</v>
+        <v>0.0004259622655808926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001847479143179953</v>
+        <v>0.0243517030030489</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000290794123429805</v>
+        <v>0.008778015151619911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001272050896659493</v>
+        <v>0.007772834040224552</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005044982535764575</v>
+        <v>0.006696291733533144</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009856271790340543</v>
+        <v>0.01080658100545406</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003311062464490533</v>
+        <v>0.02975378558039665</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005912440828979015</v>
+        <v>0.004537348169833422</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001366017153486609</v>
+        <v>0.00236940011382103</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00491370540112257</v>
+        <v>0.006954681128263474</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002366699278354645</v>
+        <v>0.02407245896756649</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000181489740498364</v>
+        <v>0.005665861070156097</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002460792602505535</v>
+        <v>0.000569202471524477</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0005628337385132909</v>
+        <v>0.01496504619717598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002450411266181618</v>
+        <v>0.0006776138907298446</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001223148545250297</v>
+        <v>0.001146517228335142</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003731781616806984</v>
+        <v>0.005559704266488552</v>
       </c>
       <c r="V5" t="n">
-        <v>9.798539394978434e-05</v>
+        <v>0.005676423199474812</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0001581549295224249</v>
+        <v>0.005478668492287397</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001017941394820809</v>
+        <v>0.004210756160318851</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001041020732372999</v>
+        <v>0.0006740702665410936</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001156056532636285</v>
+        <v>0.005684411153197289</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003376250679139048</v>
+        <v>0.003079983638599515</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001772818504832685</v>
+        <v>0.0007996277417987585</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0006572867278009653</v>
+        <v>0.005247804801911116</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0009189019328914583</v>
+        <v>0.002551584970206022</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0004323554167058319</v>
+        <v>0.005101401824504137</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0005760678905062377</v>
+        <v>0.009200685657560825</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.000831416982691735</v>
+        <v>0.004000562243163586</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.001111712190322578</v>
+        <v>0.001091980724595487</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0006333169294521213</v>
+        <v>0.01279039867222309</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5.179567961022258e-05</v>
+        <v>0.0003916210262104869</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0001214488074765541</v>
+        <v>0.003170345909893513</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.001497900811955333</v>
+        <v>0.003886648686602712</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0004745784972328693</v>
+        <v>0.005002319812774658</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.57028241828084e-05</v>
+        <v>0.005320042837411165</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.000168085825862363</v>
+        <v>0.002400738187134266</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0004423662612680346</v>
+        <v>0.002902189968153834</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0006018565618433058</v>
+        <v>0.00292171910405159</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0002472412306815386</v>
+        <v>0.007129250559955835</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0001115726045100018</v>
+        <v>0.003302404889836907</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0008169063366949558</v>
+        <v>0.008155487477779388</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.003088835859671235</v>
+        <v>0.02354004234075546</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0003495969576761127</v>
+        <v>0.00533901946619153</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0005113340448588133</v>
+        <v>0.00147465942427516</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001401781686581671</v>
+        <v>0.005676700733602047</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0008041189284995198</v>
+        <v>0.01411121804267168</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.001469797920435667</v>
+        <v>0.0001275327958865091</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.798924783244729e-05</v>
+        <v>0.001876088441349566</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001056058797985315</v>
+        <v>0.004739251919090748</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0005334689049050212</v>
+        <v>0.000592500320635736</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.000639452482573688</v>
+        <v>0.002637040568515658</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.353813948109746e-05</v>
+        <v>0.00322600663639605</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0007877579773776233</v>
+        <v>0.0002800580114126205</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.003379891160875559</v>
+        <v>0.004390117712318897</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0003393128572497517</v>
+        <v>0.006487427279353142</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001334433676674962</v>
+        <v>0.002980156801640987</v>
       </c>
       <c r="BJ5" t="n">
-        <v>5.46187802683562e-05</v>
+        <v>0.005542146041989326</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.001106438226997852</v>
+        <v>0.003880588570609689</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0008027349249459803</v>
+        <v>0.0001941208029165864</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0002385943080298603</v>
+        <v>0.006098181009292603</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0002531535865273327</v>
+        <v>0.0001677875261520967</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0004968531429767609</v>
+        <v>0.001391030731610954</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0007148910081014037</v>
+        <v>0.007018612697720528</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0008522081188857555</v>
+        <v>0.003525976091623306</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0006721585523337126</v>
+        <v>0.01089972071349621</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0004230657068546861</v>
+        <v>1.600210089236498e-05</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0001752104144543409</v>
+        <v>0.006996242329478264</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0006827128818258643</v>
+        <v>0.003251695539802313</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.002221323782578111</v>
+        <v>0.0137299969792366</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0008786103571765125</v>
+        <v>0.003292298875749111</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0006140008335933089</v>
+        <v>0.007582658901810646</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0007632382330484688</v>
+        <v>0.001707471557892859</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0005485022556968033</v>
+        <v>0.009782628156244755</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0007031222921796143</v>
+        <v>0.001628697151318192</v>
       </c>
       <c r="CB5" t="n">
-        <v>8.047834853641689e-05</v>
+        <v>0.0002058763056993484</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.000147849423228763</v>
+        <v>0.00358806736767292</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.584910544101149e-05</v>
+        <v>0.003655878361314535</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0006632370641455054</v>
+        <v>0.007205859757959843</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0002229735837318003</v>
+        <v>0.001027364516630769</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0003678590292111039</v>
+        <v>0.002019001403823495</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.000724118493963033</v>
+        <v>0.002021844731643796</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.000451636005891487</v>
+        <v>0.006288002710789442</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0005317000905051827</v>
+        <v>0.004160622600466013</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0001211593626067042</v>
+        <v>0.001514669973403215</v>
       </c>
       <c r="CL5" t="n">
-        <v>7.768734940327704e-05</v>
+        <v>0.001496198237873614</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0005681305774487555</v>
+        <v>0.0004516313783824444</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0002808749559335411</v>
+        <v>0.01272478513419628</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001527930871816352</v>
+        <v>0.004804260097444057</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0003656634944491088</v>
+        <v>0.004831936676055193</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0003437893465161324</v>
+        <v>0.005781717598438263</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0005177333950996399</v>
+        <v>0.004029645584523678</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001232137088663876</v>
+        <v>0.002426659222692251</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001302259275689721</v>
+        <v>0.003389701712876558</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0001025191231747158</v>
+        <v>0.0001590954780112952</v>
       </c>
       <c r="CV5" t="n">
-        <v>8.152732334565371e-05</v>
+        <v>0.002425786573439837</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0004025119415018708</v>
+        <v>0.006489370949566364</v>
       </c>
       <c r="CX5" t="n">
-        <v>2.169588333345018e-05</v>
+        <v>0.0007769828662276268</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0004462801443878561</v>
+        <v>0.001218466553837061</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0006604504305869341</v>
+        <v>0.00142604555003345</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0006646740366704762</v>
+        <v>0.006157784722745419</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0003276541538070887</v>
+        <v>0.002089768880978227</v>
       </c>
       <c r="DC5" t="n">
-        <v>6.688249413855374e-05</v>
+        <v>0.002633882686495781</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0002059467951767147</v>
+        <v>0.001762279076501727</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0005507191526703537</v>
+        <v>0.00232049822807312</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001380123663693666</v>
+        <v>0.007054078858345747</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0005368671263568103</v>
+        <v>0.004878098145127296</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0007598183583468199</v>
+        <v>0.0009865406900644302</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0004321004962548614</v>
+        <v>0.008744961582124233</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0004222571733407676</v>
+        <v>0.007472786121070385</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.00123209145385772</v>
+        <v>6.893998943269253e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>9.89262480288744e-05</v>
+        <v>0.00565988477319479</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.000460222247056663</v>
+        <v>0.002775298431515694</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0002046568843070418</v>
+        <v>0.002581112319603562</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.000354056857759133</v>
+        <v>0.004024929832667112</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0005167094059288502</v>
+        <v>0.003033977933228016</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001689843484200537</v>
+        <v>0.005081143695861101</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0003065277705900371</v>
+        <v>0.002026213798671961</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.001799451652914286</v>
+        <v>0.0072713871486485</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0003011820663232356</v>
+        <v>0.001614636043086648</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.324608820141293e-05</v>
+        <v>0.008183157071471214</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0002077203680528328</v>
+        <v>0.002770597115159035</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0001617276720935479</v>
+        <v>0.003250012639909983</v>
       </c>
       <c r="DX5" t="n">
-        <v>8.986119064502418e-05</v>
+        <v>0.001060763373970985</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0002110848727170378</v>
+        <v>0.002229256322607398</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.00112536083906889</v>
+        <v>0.003445874433964491</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0002977036056108773</v>
+        <v>0.002624514047056437</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0008580941939726472</v>
+        <v>0.005945648998022079</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0006367958267219365</v>
+        <v>0.0004316160338930786</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0004479370545595884</v>
+        <v>0.00503185112029314</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.196225639432669e-06</v>
+        <v>0.007874181494116783</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0004551315796561539</v>
+        <v>0.003873402485623956</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0004736351547762752</v>
+        <v>0.0002477558155078441</v>
       </c>
       <c r="EH5" t="n">
-        <v>4.530109072220512e-05</v>
+        <v>0.004331132397055626</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0004484511737246066</v>
+        <v>0.00188174715731293</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0007169602904468775</v>
+        <v>0.003909969702363014</v>
       </c>
       <c r="EK5" t="n">
-        <v>6.100528844399378e-05</v>
+        <v>0.00329102948307991</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0006534199346788228</v>
+        <v>0.002540950430557132</v>
       </c>
       <c r="EM5" t="n">
-        <v>2.697253512451425e-05</v>
+        <v>0.0002789274731185287</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0002999791468027979</v>
+        <v>0.0002057343954220414</v>
       </c>
       <c r="EO5" t="n">
-        <v>9.948081424226984e-05</v>
+        <v>0.003215388860553503</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0004574351769406348</v>
+        <v>0.002496640663594007</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0006759796524420381</v>
+        <v>0.0002645856002345681</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0008010498713701963</v>
+        <v>0.00394893903285265</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0005947073805145919</v>
+        <v>0.006358121987432241</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001216447330079973</v>
+        <v>0.007937600836157799</v>
       </c>
       <c r="EU5" t="n">
-        <v>1.128445728681982e-05</v>
+        <v>0.00060335110174492</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.000335685967002064</v>
+        <v>0.000908823567442596</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.000494394451379776</v>
+        <v>0.003126299940049648</v>
       </c>
       <c r="EX5" t="n">
-        <v>3.043664037249982e-06</v>
+        <v>0.00314335385337472</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0003850005741696805</v>
+        <v>0.008477683179080486</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001090010919142514</v>
+        <v>0.0005482936976477504</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0004930957220494747</v>
+        <v>0.001096790423616767</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0005519239930436015</v>
+        <v>0.003055343171581626</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0006363552529364824</v>
+        <v>0.005486419890075922</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0005354016902856529</v>
+        <v>0.003718792693689466</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0001089310098905116</v>
+        <v>0.002079678233712912</v>
       </c>
       <c r="FF5" t="n">
-        <v>5.237840377958491e-05</v>
+        <v>0.0004368707886897027</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002909785835072398</v>
+        <v>0.0008550764177925885</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0008855900960043073</v>
+        <v>0.009910213761031628</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0003353942593093961</v>
+        <v>0.005064353812485933</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.000891634845174849</v>
+        <v>0.00299160648137331</v>
       </c>
       <c r="FK5" t="n">
-        <v>2.249552926514298e-05</v>
+        <v>0.001750156166963279</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0004293860401958227</v>
+        <v>0.009409372694790363</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0006181845674291253</v>
+        <v>0.003276140661910176</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0001574571360833943</v>
+        <v>0.01108304876834154</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0003068822552450001</v>
+        <v>0.008161033503711224</v>
       </c>
       <c r="FP5" t="n">
-        <v>9.732347098179162e-05</v>
+        <v>0.003093140432611108</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001126060495153069</v>
+        <v>0.002880251966416836</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0003890372754540294</v>
+        <v>0.01494595222175121</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.001353885047137737</v>
+        <v>0.007839960046112537</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.000176788424141705</v>
+        <v>0.001170412986539304</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0006526487413793802</v>
+        <v>0.004139918833971024</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.00114387075882405</v>
+        <v>0.0003327064914628863</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0004781429597642273</v>
+        <v>0.008757477626204491</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0005107331671752036</v>
+        <v>0.004304498434066772</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0003333539061713964</v>
+        <v>0.004244150593876839</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0003029440995305777</v>
+        <v>0.004002444911748171</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.001504768617451191</v>
+        <v>0.003690982004627585</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0003061565803363919</v>
+        <v>0.002095189178362489</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0001102539099520072</v>
+        <v>0.008047385141253471</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0006223322125151753</v>
+        <v>0.008876590058207512</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.000267716299276799</v>
+        <v>0.0007256739772856236</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0005287525709718466</v>
+        <v>0.005333196371793747</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0005889259045943618</v>
+        <v>0.006867320276796818</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.02965192124247551</v>
+        <v>0.001740486943162978</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2796301245689392</v>
+        <v>0.0004690020577982068</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01181771419942379</v>
+        <v>0.000147958955494687</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1380021870136261</v>
+        <v>0.002801435068249702</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03132452815771103</v>
+        <v>0.0005200931918807328</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05562609061598778</v>
+        <v>0.002348884008824825</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02111396566033363</v>
+        <v>0.001866304199211299</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03952661156654358</v>
+        <v>0.00150458060670644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006146597675979137</v>
+        <v>0.0009357195231132209</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04818164557218552</v>
+        <v>0.001876967377029359</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1890419870615005</v>
+        <v>0.0003122611960861832</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01435172744095325</v>
+        <v>0.0001256954274140298</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1153348833322525</v>
+        <v>0.003970387857407331</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06124077364802361</v>
+        <v>0.00103364628739655</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07876907289028168</v>
+        <v>0.002612235955893993</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0196281336247921</v>
+        <v>0.002366848755627871</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009948364458978176</v>
+        <v>0.001201852806843817</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0125527661293745</v>
+        <v>0.001334361499175429</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01065842062234879</v>
+        <v>0.0003158190229441971</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03842803835868835</v>
+        <v>7.359334267675877e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009437172673642635</v>
+        <v>9.7190699307248e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04146381095051765</v>
+        <v>0.0002380137011641636</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02868921868503094</v>
+        <v>0.0008923066197894514</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0196227990090847</v>
+        <v>0.0006051447708159685</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03160898387432098</v>
+        <v>2.08376586670056e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03522514551877975</v>
+        <v>0.0001997473736992106</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02897336520254612</v>
+        <v>5.167404015082866e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005211172625422478</v>
+        <v>0.0004934099852107465</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03002002090215683</v>
+        <v>0.0002880179090425372</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002777946647256613</v>
+        <v>0.0004843640490435064</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.01452160812914371</v>
+        <v>8.798368799034506e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.006314744241535664</v>
+        <v>8.865545532898977e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0190393440425396</v>
+        <v>0.001359890797175467</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.009479224681854248</v>
+        <v>0.0001380824978696182</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.005831102374941111</v>
+        <v>0.00106527132447809</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01831695809960365</v>
+        <v>0.0001078393906936981</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02750327438116074</v>
+        <v>0.0006782357813790441</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03267889842391014</v>
+        <v>0.0005062054842710495</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003882485907524824</v>
+        <v>0.0002640864113345742</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01722580567002296</v>
+        <v>0.0002828095166478306</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.02108271606266499</v>
+        <v>0.0003574660804588348</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03394882008433342</v>
+        <v>0.0003316164657007903</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01205134019255638</v>
+        <v>0.0008609300712123513</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.006320668384432793</v>
+        <v>0.0001897342153824866</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.01543444860726595</v>
+        <v>1.0853716503334e-06</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01331359334290028</v>
+        <v>0.001687467913143337</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2001585960388184</v>
+        <v>0.0007139650988392532</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.003451487282291055</v>
+        <v>0.0009585477528162301</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0288989245891571</v>
+        <v>0.0008420087397098541</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0309289675205946</v>
+        <v>0.002344611100852489</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.006541717331856489</v>
+        <v>0.002075326163321733</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002796843647956848</v>
+        <v>0.0002466431760694832</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.01388660073280334</v>
+        <v>0.0003350627957843244</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.02517654374241829</v>
+        <v>0.0003167062532156706</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.606958150863647e-05</v>
+        <v>0.0001581422257004306</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0373530201613903</v>
+        <v>9.286671411246061e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.03235340118408203</v>
+        <v>0.0001948814024217427</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.005748536437749863</v>
+        <v>4.806352080777287e-05</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.07182114571332932</v>
+        <v>0.001365132629871368</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.02383254654705524</v>
+        <v>0.0005840463563799858</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0301322266459465</v>
+        <v>0.0004344077897258103</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0219181664288044</v>
+        <v>0.0008458484662696719</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01053600199520588</v>
+        <v>0.0003104395873378962</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.04110235720872879</v>
+        <v>0.0002088123001158237</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04292205721139908</v>
+        <v>0.0008233774569816887</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.00887109711766243</v>
+        <v>0.0002855974016711116</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.02432292699813843</v>
+        <v>0.00088150380179286</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0260762944817543</v>
+        <v>0.0002077075187116861</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0144073124974966</v>
+        <v>0.0004566542338579893</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.005056846421211958</v>
+        <v>0.0002209638769272715</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.006382876075804234</v>
+        <v>0.0001690909848548472</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02240821532905102</v>
+        <v>0.0002197010471718386</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.01457225158810616</v>
+        <v>0.000691498164087534</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1092411577701569</v>
+        <v>0.0002462032134644687</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01247992552816868</v>
+        <v>0.0002128285996150225</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.025228226557374</v>
+        <v>0.001527280663140118</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.002885629422962666</v>
+        <v>0.0008795925532467663</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.04130132496356964</v>
+        <v>0.0008751060231588781</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.01691419258713722</v>
+        <v>0.0002349374117329717</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01009534019976854</v>
+        <v>6.120094622019678e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.03057858161628246</v>
+        <v>6.432140799006447e-05</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0175983440130949</v>
+        <v>0.0005594221875071526</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.04309675842523575</v>
+        <v>2.069486072286963e-06</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.01720555126667023</v>
+        <v>0.0001868699764600024</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01310017518699169</v>
+        <v>0.0009042980382218957</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01063610799610615</v>
+        <v>0.0002133719390258193</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01519928965717554</v>
+        <v>0.0002850320597644895</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.009104195982217789</v>
+        <v>6.626198592130095e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.007431811653077602</v>
+        <v>0.0002688661043066531</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.01627289317548275</v>
+        <v>0.0001993487530853599</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.03200317174196243</v>
+        <v>0.000552830402739346</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.00994779821485281</v>
+        <v>0.0003692973114084452</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0177827961742878</v>
+        <v>0.001091868267394602</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.06085002794861794</v>
+        <v>0.001070669502951205</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.04363780468702316</v>
+        <v>0.0003497562720440328</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.03068024106323719</v>
+        <v>0.0005785261164419353</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.03122838586568832</v>
+        <v>0.0004867033567279577</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0363064780831337</v>
+        <v>0.000628377019893378</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.01448883954435587</v>
+        <v>0.0001176156074507162</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.01600195094943047</v>
+        <v>0.0005223671323619783</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.03654805943369865</v>
+        <v>2.538708213251084e-05</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.01624637097120285</v>
+        <v>0.0002756576868705451</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02715828269720078</v>
+        <v>0.001029816223308444</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0125964405015111</v>
+        <v>0.0004955072654411197</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0203779861330986</v>
+        <v>0.0004072024603374302</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01167776994407177</v>
+        <v>0.0001357002911390737</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.01280402392148972</v>
+        <v>0.0001639002293813974</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01028482150286436</v>
+        <v>0.0003257738426327705</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0200421679764986</v>
+        <v>0.0008868742734193802</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.02261208929121494</v>
+        <v>0.0001578610390424728</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.007741263601928949</v>
+        <v>6.75507471896708e-05</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.05523459985852242</v>
+        <v>0.0007415759610012174</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03443797677755356</v>
+        <v>0.001379438326694071</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.01954862102866173</v>
+        <v>0.001604721765033901</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.02396809868514538</v>
+        <v>0.0002739424526225775</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.01743764244019985</v>
+        <v>0.001331135630607605</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.001923789153806865</v>
+        <v>0.0001708005147520453</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.02554923482239246</v>
+        <v>0.0002567653427831829</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0175214484333992</v>
+        <v>0.000337388482876122</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0194036141037941</v>
+        <v>0.0003295318456366658</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0003169002011418343</v>
+        <v>0.0002009260206250474</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01403148379176855</v>
+        <v>0.0001863321813289076</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.03733140975236893</v>
+        <v>0.0006019868305884302</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.003872786182910204</v>
+        <v>0.0002994488459080458</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.01046307012438774</v>
+        <v>0.0005140314460732043</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.02772538736462593</v>
+        <v>0.001129525830037892</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.01477988995611668</v>
+        <v>0.0003745028225239366</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.005609262734651566</v>
+        <v>0.0003479809092823416</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.04193592071533203</v>
+        <v>0.001048904261551797</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.006430414505302906</v>
+        <v>0.0006920197629369795</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0326077826321125</v>
+        <v>0.0006358242244459689</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.00607738085091114</v>
+        <v>0.0003706252900883555</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.002747897058725357</v>
+        <v>0.0007881296332925558</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.01023751124739647</v>
+        <v>0.0006924292538315058</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.007491324096918106</v>
+        <v>0.0002329547423869371</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.006020964123308659</v>
+        <v>0.001062450697645545</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.01724736019968987</v>
+        <v>1.163065462606028e-06</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.003786101937294006</v>
+        <v>0.0001817670708987862</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.006711291614919901</v>
+        <v>0.001045532175339758</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.004501397721469402</v>
+        <v>6.643899723712821e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01175273396074772</v>
+        <v>0.0002068833564408123</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.01007944345474243</v>
+        <v>0.0001073088715202175</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.003111171303316951</v>
+        <v>7.151458703447133e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.004182353615760803</v>
+        <v>5.86848909733817e-05</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.01073329336941242</v>
+        <v>0.0004400295438244939</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.02612845972180367</v>
+        <v>0.0003451990778557956</v>
       </c>
       <c r="EQ7" t="n">
-        <v>1.923367381095886e-05</v>
+        <v>0.0005167519557289779</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.02470270171761513</v>
+        <v>0.001141127431765199</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.03006988391280174</v>
+        <v>0.0001978147483896464</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.07647784799337387</v>
+        <v>0.0004661956336349249</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.02276900969445705</v>
+        <v>0.0004741521552205086</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.03661127015948296</v>
+        <v>0.0002776236215140671</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.009920995682477951</v>
+        <v>0.001987863797694445</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.01284582726657391</v>
+        <v>0.000619292666669935</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.03466379269957542</v>
+        <v>8.782686199992895e-05</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.006987895350903273</v>
+        <v>6.044738256605342e-05</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02021189592778683</v>
+        <v>0.001032417290844023</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.009909754619002342</v>
+        <v>0.0002940522390417755</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.01898602955043316</v>
+        <v>0.0004088591085746884</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.01535413507372141</v>
+        <v>0.0002336145553272218</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.007146644871681929</v>
+        <v>0.0002715378068387508</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01575145870447159</v>
+        <v>0.0001041612558765337</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.00809889379888773</v>
+        <v>6.944087363081053e-05</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02476220577955246</v>
+        <v>0.0003236614866182208</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.01575331948697567</v>
+        <v>0.0005379329668357968</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03214205428957939</v>
+        <v>0.00015886256005615</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.004697933327406645</v>
+        <v>8.408605208387598e-05</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.003053451422601938</v>
+        <v>0.000135533613502048</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.008546260185539722</v>
+        <v>0.0003708400763571262</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.01476478856056929</v>
+        <v>0.000468995189294219</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.02506338059902191</v>
+        <v>0.0009238377097062767</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.01478239241987467</v>
+        <v>0.000279839732684195</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.01109595317393541</v>
+        <v>0.0002149469510186464</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001339440350420773</v>
+        <v>0.0008929671603254974</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01989839226007462</v>
+        <v>0.0008522180141881108</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04639426246285439</v>
+        <v>0.0007230218034237623</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.01874558068811893</v>
+        <v>0.0001070927974069491</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.01067016087472439</v>
+        <v>0.0003093264240305871</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.01277755480259657</v>
+        <v>0.003057786962017417</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.008286359719932079</v>
+        <v>0.0003781693812925369</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.03620614483952522</v>
+        <v>0.0001801036996766925</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01184570509940386</v>
+        <v>0.0003387002216186374</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.01866648346185684</v>
+        <v>0.0008548105834051967</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.00514733511954546</v>
+        <v>0.001429872587323189</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.04180709272623062</v>
+        <v>0.0007464673835784197</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.02739789336919785</v>
+        <v>0.00137703528162092</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.0855780765414238</v>
+        <v>0.0006554059218615294</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.01076837908476591</v>
+        <v>0.0001463449880247936</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01977668888866901</v>
+        <v>0.0008602016023360193</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.001222542603500187</v>
+        <v>0.01238765940070152</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003434331621974707</v>
+        <v>0.02781609073281288</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001579540898092091</v>
+        <v>0.01527129579335451</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001854207832366228</v>
+        <v>0.004706095438450575</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009258848614990711</v>
+        <v>0.03385116159915924</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02298036962747574</v>
+        <v>0.06170697137713432</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002398148644715548</v>
+        <v>0.02084083296358585</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004518329631537199</v>
+        <v>0.04837772622704506</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009983333759009838</v>
+        <v>0.0004339837469160557</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002211456187069416</v>
+        <v>0.00185768585652113</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00225822115316987</v>
+        <v>0.03930972889065742</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005212149117141962</v>
+        <v>0.02029863372445107</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003243703860789537</v>
+        <v>0.0008881053654477</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003120163688436151</v>
+        <v>0.04205256327986717</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01921212114393711</v>
+        <v>0.06478036195039749</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004322497174143791</v>
+        <v>0.02941878885030746</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009190855547785759</v>
+        <v>0.03927561268210411</v>
       </c>
       <c r="R9" t="n">
-        <v>0.006314297672361135</v>
+        <v>0.0114465020596981</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002084495732560754</v>
+        <v>0.007979417219758034</v>
       </c>
       <c r="T9" t="n">
-        <v>0.000376743875676766</v>
+        <v>0.009853978641331196</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0003121604968328029</v>
+        <v>0.009160824120044708</v>
       </c>
       <c r="V9" t="n">
-        <v>0.005012697540223598</v>
+        <v>0.01248349063098431</v>
       </c>
       <c r="W9" t="n">
-        <v>0.005266884807497263</v>
+        <v>0.005338922142982483</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001220784266479313</v>
+        <v>0.004337236750870943</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002171406522393227</v>
+        <v>0.008764299564063549</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0006678877980448306</v>
+        <v>0.002230900572612882</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00230210367590189</v>
+        <v>0.003005304839462042</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0006090187816880643</v>
+        <v>0.003208879148587584</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.003935227170586586</v>
+        <v>0.02044013887643814</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.006832437589764595</v>
+        <v>0.002011044416576624</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0009182840585708618</v>
+        <v>0.01080671697854996</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0002258195891045034</v>
+        <v>0.01975492015480995</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.000922297709621489</v>
+        <v>0.002314903773367405</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.007178422063589096</v>
+        <v>0.005744412075728178</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.002787460573017597</v>
+        <v>0.01580560579895973</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0002920593833550811</v>
+        <v>0.003330466337502003</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.002218947978690267</v>
+        <v>0.007938873954117298</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0003649417776614428</v>
+        <v>0.01003872975707054</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001119042048230767</v>
+        <v>0.003706355579197407</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001206984394229949</v>
+        <v>0.002126030158251524</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002380813006311655</v>
+        <v>0.01080052927136421</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002086285268887877</v>
+        <v>0.003096743952482939</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.001801906153559685</v>
+        <v>0.002406988758593798</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.001260600867681205</v>
+        <v>0.008512741886079311</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001457487815059721</v>
+        <v>0.002722922945395112</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.234424654394388e-05</v>
+        <v>0.005917442962527275</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.006155123002827168</v>
+        <v>0.07899060100317001</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0003756427904590964</v>
+        <v>0.01049290411174297</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.005333003588020802</v>
+        <v>0.0131020825356245</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.01439454033970833</v>
+        <v>0.004611550830304623</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.008631505072116852</v>
+        <v>0.02131206542253494</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001780567923560739</v>
+        <v>0.00329634128138423</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001734070014208555</v>
+        <v>0.01577384956181049</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.006750458851456642</v>
+        <v>0.009418345987796783</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.00176434509921819</v>
+        <v>0.01854030787944794</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00240204157307744</v>
+        <v>0.02948735281825066</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.004155708942562342</v>
+        <v>0.006173679605126381</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0007512918673455715</v>
+        <v>0.01377581432461739</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.00194845162332058</v>
+        <v>0.0322936624288559</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.008334114216268063</v>
+        <v>0.001961755333468318</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002120485529303551</v>
+        <v>9.988807141780853e-05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0001643643481656909</v>
+        <v>0.01492726150900126</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.00107114645652473</v>
+        <v>0.0002247198717668653</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001331997802481055</v>
+        <v>0.00968701858073473</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.008179060183465481</v>
+        <v>0.01910917088389397</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.00306284474208951</v>
+        <v>0.01853536069393158</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0007578406948596239</v>
+        <v>0.00758176576346159</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002990091685205698</v>
+        <v>0.008736507967114449</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0009721954120323062</v>
+        <v>0.01348124071955681</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00306197558529675</v>
+        <v>0.02601869776844978</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.002823992865160108</v>
+        <v>0.0003899834118783474</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.003494348376989365</v>
+        <v>0.001430799602530897</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0005857343203388155</v>
+        <v>0.0009542302577756345</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003680621972307563</v>
+        <v>0.03510092571377754</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.001652105594985187</v>
+        <v>0.008951649069786072</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002712541958317161</v>
+        <v>0.002267554402351379</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.006249121390283108</v>
+        <v>0.002161600161343813</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.005932591389864683</v>
+        <v>0.0122959315776825</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.001505483873188496</v>
+        <v>0.01140990667045116</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0007159113883972168</v>
+        <v>0.009920510463416576</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.966897101141512e-05</v>
+        <v>0.0006971531547605991</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0009299317025579512</v>
+        <v>0.00118231913074851</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001579114585183561</v>
+        <v>0.00780666247010231</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0007930154097266495</v>
+        <v>0.002854825928807259</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0005165428156033158</v>
+        <v>0.0004816537257283926</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001373947830870748</v>
+        <v>0.01082537136971951</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.004384465515613556</v>
+        <v>0.0151100717484951</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0007595813367515802</v>
+        <v>0.0100103123113513</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001784298568964005</v>
+        <v>0.006360484752804041</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0004259516717866063</v>
+        <v>0.002399766584858298</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0006868701311759651</v>
+        <v>0.005426003597676754</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.00337357958778739</v>
+        <v>0.02300992980599403</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001517335069365799</v>
+        <v>0.004778520669788122</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.002994039095938206</v>
+        <v>0.01324823498725891</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.00740730669349432</v>
+        <v>0.01645662635564804</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.001403312082402408</v>
+        <v>0.01981369778513908</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001543040620163083</v>
+        <v>0.009823422878980637</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.002721026539802551</v>
+        <v>0.009660245850682259</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.002260929672047496</v>
+        <v>0.01444344036281109</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.000172406726051122</v>
+        <v>0.004565354436635971</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001871247892268002</v>
+        <v>0.0066661830060184</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.001048141857609153</v>
+        <v>0.004808743018656969</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0004918414051644504</v>
+        <v>0.0009835879318416119</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.002200457267463207</v>
+        <v>0.01178812049329281</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.00410230690613389</v>
+        <v>0.01509624533355236</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001000826247036457</v>
+        <v>0.006861784495413303</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.002608034992590547</v>
+        <v>0.004039039369672537</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0009310069726780057</v>
+        <v>0.002713869325816631</v>
       </c>
       <c r="DE9" t="n">
-        <v>6.248807767406106e-05</v>
+        <v>0.01274801418185234</v>
       </c>
       <c r="DF9" t="n">
-        <v>8.06024982011877e-05</v>
+        <v>0.002188190352171659</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.002040587598457932</v>
+        <v>0.007794584147632122</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.00552046112716198</v>
+        <v>0.001559512922540307</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.005191465839743614</v>
+        <v>0.01135806366801262</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.00628377590328455</v>
+        <v>0.001477713463827968</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0009313199552707374</v>
+        <v>0.006782006472349167</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.003347514430060983</v>
+        <v>0.008493543602526188</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.009031947702169418</v>
+        <v>0.02006278932094574</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.003108886536210775</v>
+        <v>0.000317468773573637</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.00170838856138289</v>
+        <v>0.001993014011532068</v>
       </c>
       <c r="DP9" t="n">
-        <v>5.132853402756155e-05</v>
+        <v>0.0005876522045582533</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0007385241333395243</v>
+        <v>0.01008728612214327</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.002550570527091622</v>
+        <v>0.003625775454565883</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.000957280455622822</v>
+        <v>0.007888631895184517</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001220596837811172</v>
+        <v>0.005262142978608608</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.002700908575206995</v>
+        <v>0.001873505301773548</v>
       </c>
       <c r="DV9" t="n">
-        <v>3.155681770294905e-05</v>
+        <v>0.01213055849075317</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0006217800546437502</v>
+        <v>0.00897729117423296</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0007734349928796291</v>
+        <v>0.00867655873298645</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.002839806489646435</v>
+        <v>0.008591918274760246</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.002216425025835633</v>
+        <v>0.00422401400282979</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0005714551080018282</v>
+        <v>0.003496300196275115</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.002285319846123457</v>
+        <v>0.001768492395058274</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.002061486709862947</v>
+        <v>0.007898162119090557</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.003441051580011845</v>
+        <v>0.00440625287592411</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.001702685607597232</v>
+        <v>0.007140670903027058</v>
       </c>
       <c r="EF9" t="n">
-        <v>9.264366235584021e-05</v>
+        <v>0.003428427968174219</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.002998437965288758</v>
+        <v>0.001847082399763167</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001024325494654477</v>
+        <v>0.005044646561145782</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0007345298654399812</v>
+        <v>0.008829951286315918</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001001970493234694</v>
+        <v>0.005398775916546583</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.004754068795591593</v>
+        <v>0.01577488519251347</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001975100603885949</v>
+        <v>0.008824704214930534</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.001444098772481084</v>
+        <v>0.001896057743579149</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.00142889132257551</v>
+        <v>0.006221292540431023</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0009321619290858507</v>
+        <v>0.00716001819819212</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001547733205370605</v>
+        <v>0.003446075599640608</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001761005725711584</v>
+        <v>0.001628724508918822</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.00141392822843045</v>
+        <v>0.008886479772627354</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0007393489358946681</v>
+        <v>0.01523259282112122</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.002084659412503242</v>
+        <v>0.01425882987678051</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001035299617797136</v>
+        <v>0.01147725433111191</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.01055486965924501</v>
+        <v>0.008929219096899033</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.001680273562669754</v>
+        <v>0.005408629775047302</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0002723140059970319</v>
+        <v>0.002229774603620172</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.002118893433362246</v>
+        <v>0.008782234042882919</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0004513111198320985</v>
+        <v>0.002791001927107573</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0007036135066300631</v>
+        <v>0.0005398500943556428</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.002103951293975115</v>
+        <v>0.009293701499700546</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.003575448179617524</v>
+        <v>0.01537033915519714</v>
       </c>
       <c r="FD9" t="n">
-        <v>2.694374416023493e-05</v>
+        <v>0.01071341708302498</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.002516040578484535</v>
+        <v>0.00584558816626668</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0002384137769695371</v>
+        <v>8.365139365196228e-06</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.002067710738629103</v>
+        <v>0.0099343191832304</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001704306458123028</v>
+        <v>0.00806611031293869</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.00129035918507725</v>
+        <v>0.004377956502139568</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.003705296665430069</v>
+        <v>0.01405088696628809</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001859494368545711</v>
+        <v>0.005752784200012684</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.002388410270214081</v>
+        <v>0.004196675028651953</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0004664447624236345</v>
+        <v>0.006380346603691578</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.004575463011860847</v>
+        <v>0.01128342561423779</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.001741447602398694</v>
+        <v>0.002016058191657066</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0004067593836225569</v>
+        <v>0.0002351673319935799</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.004268188495188951</v>
+        <v>0.01671750098466873</v>
       </c>
       <c r="FR9" t="n">
-        <v>7.282651495188475e-05</v>
+        <v>0.01213619392365217</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.003722867928445339</v>
+        <v>0.01243737619370222</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.002912767231464386</v>
+        <v>0.03181907162070274</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.004966877400875092</v>
+        <v>0.003978623077273369</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.005505582317709923</v>
+        <v>0.009896213188767433</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.00077079888433218</v>
+        <v>0.01296450290828943</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.001956162974238396</v>
+        <v>0.007976334542036057</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.002264649840071797</v>
+        <v>0.00121063319966197</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0002336418547201902</v>
+        <v>0.006556532345712185</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.003939162474125624</v>
+        <v>0.0251280702650547</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0009358953684568405</v>
+        <v>3.757467493414879e-05</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.00583349633961916</v>
+        <v>0.01503454614430666</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0003824132727459073</v>
+        <v>0.001132461591623724</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.003754069097340107</v>
+        <v>0.01948044821619987</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.003955066204071045</v>
+        <v>0.0001736045815050602</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.002608340932056308</v>
+        <v>0.001452141557820141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.00326647493056953</v>
+        <v>0.001444365014322102</v>
       </c>
       <c r="B10" t="n">
-        <v>0.04848218709230423</v>
+        <v>0.0273023396730423</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002187465783208609</v>
+        <v>0.004598207771778107</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01790141686797142</v>
+        <v>0.003623506519943476</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004668010864406824</v>
+        <v>0.009530715644359589</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03632450103759766</v>
+        <v>0.02862209640443325</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002597357844933867</v>
+        <v>0.006118962541222572</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01701233349740505</v>
+        <v>0.03549113497138023</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001692375750280917</v>
+        <v>0.01335312053561211</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01064796093851328</v>
+        <v>0.006002703681588173</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04202982783317566</v>
+        <v>0.03277472779154778</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001617562840692699</v>
+        <v>0.01042644586414099</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01969591155648232</v>
+        <v>0.01091102790087461</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0001974058104678988</v>
+        <v>0.03677736595273018</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03394367918372154</v>
+        <v>0.03829485550522804</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004825852811336517</v>
+        <v>0.004189635626971722</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.004890351556241512</v>
+        <v>0.02925083041191101</v>
       </c>
       <c r="R10" t="n">
-        <v>0.004124992061406374</v>
+        <v>0.01640897803008556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.000497363624162972</v>
+        <v>0.002222608076408505</v>
       </c>
       <c r="T10" t="n">
-        <v>0.002616744954138994</v>
+        <v>0.01165430061519146</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002275341656059027</v>
+        <v>0.004030896350741386</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004216319881379604</v>
+        <v>0.01210318319499493</v>
       </c>
       <c r="W10" t="n">
-        <v>0.006824586074799299</v>
+        <v>0.005127810873091221</v>
       </c>
       <c r="X10" t="n">
-        <v>0.006532473023980856</v>
+        <v>0.008180547505617142</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003442678134888411</v>
+        <v>0.003305173246189952</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00551244942471385</v>
+        <v>0.006316315848380327</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00490192836150527</v>
+        <v>0.001934725325554609</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001185087719932199</v>
+        <v>0.01218889374285936</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.003592978231608868</v>
+        <v>0.007056597620248795</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001202821731567383</v>
+        <v>0.001817986601963639</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.003488541813567281</v>
+        <v>0.01155089866369963</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0006879392312839627</v>
+        <v>0.01910154893994331</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002729927422478795</v>
+        <v>0.007220491301268339</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0007923586526885629</v>
+        <v>0.0008365556132048368</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.002377745695412159</v>
+        <v>0.008232961408793926</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001052958192303777</v>
+        <v>0.007096318062394857</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.00451175682246685</v>
+        <v>0.005641673691570759</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.005374717060476542</v>
+        <v>0.01577099598944187</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0006826194003224373</v>
+        <v>0.004906164482235909</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.003109892597422004</v>
+        <v>0.001522082835435867</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.00527254631742835</v>
+        <v>0.005428015254437923</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.008006338030099869</v>
+        <v>0.006654337514191866</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.002049709437415004</v>
+        <v>0.001186352455988526</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.003053969005122781</v>
+        <v>0.007851285859942436</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.00502926716580987</v>
+        <v>0.002809621626511216</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.004778654314577579</v>
+        <v>0.001399051630869508</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.03131197392940521</v>
+        <v>0.06751053035259247</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.004866488743573427</v>
+        <v>0.0009894706308841705</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0009973263368010521</v>
+        <v>0.001537315314635634</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.004126975778490305</v>
+        <v>0.002496266504749656</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02068138867616653</v>
+        <v>0.02581659890711308</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.006527981255203485</v>
+        <v>0.001379108522087336</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.00832858495414257</v>
+        <v>0.01205943990498781</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0097507294267416</v>
+        <v>0.004638674203306437</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.004357059486210346</v>
+        <v>0.004363055340945721</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00908393133431673</v>
+        <v>0.02881903201341629</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.008687102235853672</v>
+        <v>0.0003119626780971885</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.005221866071224213</v>
+        <v>0.004884572234004736</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.009419101290404797</v>
+        <v>0.008487040176987648</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01138282101601362</v>
+        <v>0.007808881346136332</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.004825131502002478</v>
+        <v>0.002335447818040848</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.004234411288052797</v>
+        <v>0.01053988002240658</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.002072033006697893</v>
+        <v>0.007576178759336472</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.001542588230222464</v>
+        <v>0.004322256427258253</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.007863626815378666</v>
+        <v>0.007942500524222851</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001434010453522205</v>
+        <v>0.01251651719212532</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.002976469229906797</v>
+        <v>0.0001567690633237362</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0009895055554807186</v>
+        <v>0.01031295023858547</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001379390014335513</v>
+        <v>0.005767679307609797</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.001809749519452453</v>
+        <v>0.004900627303868532</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0003638268681243062</v>
+        <v>0.001581784221343696</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.00241646496579051</v>
+        <v>0.006154042668640614</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.003140769433230162</v>
+        <v>0.004694304428994656</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.01635713502764702</v>
+        <v>0.02872722595930099</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.004330795258283615</v>
+        <v>0.0005423331749625504</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.002244230592623353</v>
+        <v>0.01089358050376177</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0002678670571185648</v>
+        <v>0.01093940809369087</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.01040007267147303</v>
+        <v>0.01718108169734478</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0004146815044805408</v>
+        <v>0.008863051421940327</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003803190542384982</v>
+        <v>0.009408245794475079</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.005282261874526739</v>
+        <v>0.001114068203605711</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0007206815062090755</v>
+        <v>0.001587582984939218</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.007109072525054216</v>
+        <v>0.01029723417013884</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.003044365672394633</v>
+        <v>0.00364528177306056</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002860957058146596</v>
+        <v>0.002106016967445612</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0002972191723529249</v>
+        <v>0.004937847144901752</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.004606185480952263</v>
+        <v>0.006795123685151339</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.003192631062120199</v>
+        <v>0.002949191024526954</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.00262359413318336</v>
+        <v>0.001720892847515643</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.003595386864617467</v>
+        <v>0.0005333395674824715</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.005911034066230059</v>
+        <v>0.0002311915159225464</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.002527456730604172</v>
+        <v>0.01622602343559265</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0009475368424318731</v>
+        <v>0.0009224605746567249</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.006910126656293869</v>
+        <v>0.01816994696855545</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.000536338600795716</v>
+        <v>0.01173054426908493</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.001945273019373417</v>
+        <v>0.004968767985701561</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.007494259160012007</v>
+        <v>0.002013536635786295</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.006062099244445562</v>
+        <v>0.01037136372178793</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0005042116390541196</v>
+        <v>0.001074555795639753</v>
       </c>
       <c r="CV10" t="n">
-        <v>9.829527698457241e-06</v>
+        <v>0.001432413700968027</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.006398907396942377</v>
+        <v>0.008682303130626678</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.003321805037558079</v>
+        <v>0.003695468418300152</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0043366439640522</v>
+        <v>0.004381423350423574</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.001054828288033605</v>
+        <v>0.00561514962464571</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.005604279227554798</v>
+        <v>0.009825876913964748</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.002512924140319228</v>
+        <v>0.0002192698593717068</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.00444812560454011</v>
+        <v>0.001235966919921339</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.002850395627319813</v>
+        <v>0.0006145662628114223</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.000234341889154166</v>
+        <v>0.004118659533560276</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.006037120707333088</v>
+        <v>0.01056711561977863</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.002551864366978407</v>
+        <v>0.002215331187471747</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01583707332611084</v>
+        <v>0.00622833427041769</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.007540635298937559</v>
+        <v>0.01063043158501387</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.009876878000795841</v>
+        <v>0.01234943326562643</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.005709083285182714</v>
+        <v>0.009348951280117035</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.00931661669164896</v>
+        <v>0.003763481043279171</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.005952263250946999</v>
+        <v>0.003936033695936203</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0007685098680667579</v>
+        <v>0.001035939669236541</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.003283271100372076</v>
+        <v>0.008313128724694252</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0001713576493784785</v>
+        <v>0.005130181554704905</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0001395517610944808</v>
+        <v>0.005021448247134686</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0002575437829364091</v>
+        <v>0.006876843981444836</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.002996916184201837</v>
+        <v>0.009798490442335606</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.002023401902988553</v>
+        <v>0.004655214957892895</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.001300733187235892</v>
+        <v>0.0002651548711583018</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.003532025031745434</v>
+        <v>0.007622646633535624</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.001191945746541023</v>
+        <v>0.00665957061573863</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.001933537889271975</v>
+        <v>0.01240868493914604</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.00248065940104425</v>
+        <v>0.008653627708554268</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.002911754418164492</v>
+        <v>0.001461348962038755</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.001063233357854187</v>
+        <v>0.005980906542390585</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.004491161555051804</v>
+        <v>0.001688695745542645</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0004807454533874989</v>
+        <v>0.002666670829057693</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0004532112507149577</v>
+        <v>0.00845564529299736</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.006098481826484203</v>
+        <v>0.01023908704519272</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.001566520077176392</v>
+        <v>0.001148860435932875</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.005305588245391846</v>
+        <v>0.007610433269292116</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.001721352455206215</v>
+        <v>0.004660728387534618</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0004813678096979856</v>
+        <v>0.001948896795511246</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.002709752414375544</v>
+        <v>0.005006900057196617</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0008336987812072039</v>
+        <v>0.003343693912029266</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.004160656593739986</v>
+        <v>0.001613794360309839</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.001820030738599598</v>
+        <v>0.006062277127057314</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0004742569581139833</v>
+        <v>0.00120171345770359</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0004954946925863624</v>
+        <v>0.003183318767696619</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.003876011818647385</v>
+        <v>0.009143130853772163</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.004322228487581015</v>
+        <v>0.00590413948521018</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.00261489232070744</v>
+        <v>0.002413149923086166</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.002895067911595106</v>
+        <v>0.001766908448189497</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0004171559703536332</v>
+        <v>0.005403034389019012</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.004572216887027025</v>
+        <v>0.0006003065500408411</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.009230108931660652</v>
+        <v>2.901774132624269e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.001448959344998002</v>
+        <v>0.005046692211180925</v>
       </c>
       <c r="EX10" t="n">
-        <v>4.593687481246889e-05</v>
+        <v>7.953634485602379e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.006196573376655579</v>
+        <v>0.01133907865732908</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0022205023560673</v>
+        <v>0.002498119371011853</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.002409565728157759</v>
+        <v>0.004371822811663151</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001421943888999522</v>
+        <v>0.002339304657652974</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.004341259598731995</v>
+        <v>0.008715677075088024</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.005046715028584003</v>
+        <v>0.00364663521759212</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.002721197903156281</v>
+        <v>0.001784348743967712</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.004458659794181585</v>
+        <v>3.036882844753563e-06</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.002800673712044954</v>
+        <v>0.001156508456915617</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.003487054724246264</v>
+        <v>0.004973897710442543</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001051086816005409</v>
+        <v>0.006331627257168293</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.009219763800501823</v>
+        <v>0.006871672347187996</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.00179797550663352</v>
+        <v>0.001989257521927357</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.002803782466799021</v>
+        <v>0.01000801287591457</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.000234522856771946</v>
+        <v>0.006602645851671696</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.001572730951011181</v>
+        <v>0.00225482857786119</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.002656008116900921</v>
+        <v>0.01298181805759668</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.004005849361419678</v>
+        <v>0.005224830936640501</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.006193743553012609</v>
+        <v>0.0004475251771509647</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.004750174470245838</v>
+        <v>0.01302660070359707</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.00476810010150075</v>
+        <v>0.01142703648656607</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0008880685199983418</v>
+        <v>0.01535536348819733</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.002316673286259174</v>
+        <v>0.01237749680876732</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.004454992711544037</v>
+        <v>0.01309217698872089</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.00150630809366703</v>
+        <v>0.01596356928348541</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.003835431998595595</v>
+        <v>0.01603144407272339</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.006758212111890316</v>
+        <v>0.007602190133184195</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.001246098661795259</v>
+        <v>0.0004156960058026016</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.005774445831775665</v>
+        <v>0.01050360314548016</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.001233784598298371</v>
+        <v>0.002167349215596914</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.003722600173205137</v>
+        <v>0.006689050234854221</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.003594804555177689</v>
+        <v>0.003395987674593925</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0154500063508749</v>
+        <v>0.005646276287734509</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.001542559009976685</v>
+        <v>0.003183376509696245</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.002568569267168641</v>
+        <v>0.002922533545643091</v>
       </c>
     </row>
     <row r="11">
